--- a/QuoteDeveloper/cotizaciones/avicampo/Avicampo - Cotizacion.xlsx
+++ b/QuoteDeveloper/cotizaciones/avicampo/Avicampo - Cotizacion.xlsx
@@ -1054,340 +1054,344 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="85">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="6" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="18" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="18" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="18" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="18" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="18" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="18" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="18" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="18" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="18" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="18" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="18" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="18" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="18" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="8" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="18" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="18" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="17" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="6" fillId="17" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="17" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="6" fillId="17" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="18" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="4" fillId="18" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="18" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="4" fillId="18" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="19" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="19" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="20" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="20" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="20" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="4" fillId="20" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="20" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="20" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="20" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="6" fillId="20" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7746,7 +7750,10 @@
       <c r="V122" s="15"/>
       <c r="W122" s="15"/>
       <c r="X122" s="15"/>
-      <c r="Y122" s="15"/>
+      <c r="Y122" s="15" t="n">
+        <f aca="false">Y1/0.6</f>
+        <v>50885919.6969697</v>
+      </c>
       <c r="Z122" s="15"/>
       <c r="AA122" s="15"/>
       <c r="AB122" s="15"/>
@@ -8505,928 +8512,928 @@
       <c r="AE137" s="15"/>
     </row>
     <row r="138" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A138" s="22"/>
-      <c r="B138" s="22"/>
-      <c r="C138" s="22"/>
-      <c r="D138" s="22"/>
-      <c r="E138" s="22"/>
-      <c r="F138" s="22"/>
-      <c r="G138" s="22"/>
-      <c r="H138" s="22"/>
-      <c r="I138" s="22"/>
-      <c r="J138" s="22"/>
-      <c r="K138" s="22"/>
-      <c r="L138" s="22"/>
-      <c r="M138" s="22"/>
-      <c r="N138" s="22"/>
-      <c r="O138" s="22"/>
-      <c r="P138" s="22"/>
-      <c r="Q138" s="22"/>
-      <c r="R138" s="22"/>
-      <c r="S138" s="22"/>
-      <c r="T138" s="22"/>
-      <c r="U138" s="22"/>
-      <c r="V138" s="22"/>
-      <c r="W138" s="22"/>
-      <c r="X138" s="22"/>
-      <c r="Y138" s="22"/>
-      <c r="Z138" s="22"/>
-      <c r="AA138" s="22"/>
-      <c r="AB138" s="22"/>
-      <c r="AC138" s="67"/>
-      <c r="AD138" s="22"/>
-      <c r="AE138" s="22"/>
+      <c r="A138" s="67"/>
+      <c r="B138" s="67"/>
+      <c r="C138" s="67"/>
+      <c r="D138" s="67"/>
+      <c r="E138" s="67"/>
+      <c r="F138" s="67"/>
+      <c r="G138" s="67"/>
+      <c r="H138" s="67"/>
+      <c r="I138" s="67"/>
+      <c r="J138" s="67"/>
+      <c r="K138" s="67"/>
+      <c r="L138" s="67"/>
+      <c r="M138" s="67"/>
+      <c r="N138" s="67"/>
+      <c r="O138" s="67"/>
+      <c r="P138" s="67"/>
+      <c r="Q138" s="67"/>
+      <c r="R138" s="67"/>
+      <c r="S138" s="67"/>
+      <c r="T138" s="67"/>
+      <c r="U138" s="67"/>
+      <c r="V138" s="67"/>
+      <c r="W138" s="67"/>
+      <c r="X138" s="67"/>
+      <c r="Y138" s="67"/>
+      <c r="Z138" s="67"/>
+      <c r="AA138" s="67"/>
+      <c r="AB138" s="67"/>
+      <c r="AC138" s="68"/>
+      <c r="AD138" s="67"/>
+      <c r="AE138" s="67"/>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A139" s="22"/>
-      <c r="B139" s="22"/>
-      <c r="C139" s="68"/>
-      <c r="D139" s="68"/>
-      <c r="E139" s="68"/>
-      <c r="F139" s="68"/>
-      <c r="G139" s="69"/>
-      <c r="H139" s="69"/>
-      <c r="I139" s="69"/>
-      <c r="J139" s="69"/>
-      <c r="K139" s="69"/>
-      <c r="L139" s="70"/>
-      <c r="M139" s="70"/>
-      <c r="N139" s="70"/>
-      <c r="O139" s="70"/>
-      <c r="P139" s="69"/>
-      <c r="Q139" s="69"/>
-      <c r="R139" s="69"/>
-      <c r="S139" s="69"/>
-      <c r="T139" s="70"/>
-      <c r="U139" s="70"/>
-      <c r="V139" s="70"/>
-      <c r="W139" s="70"/>
-      <c r="X139" s="69"/>
-      <c r="Y139" s="69"/>
-      <c r="Z139" s="69"/>
-      <c r="AA139" s="70"/>
-      <c r="AB139" s="70"/>
-      <c r="AC139" s="70"/>
-      <c r="AD139" s="70"/>
-      <c r="AE139" s="22"/>
+      <c r="A139" s="67"/>
+      <c r="B139" s="67"/>
+      <c r="C139" s="69"/>
+      <c r="D139" s="69"/>
+      <c r="E139" s="69"/>
+      <c r="F139" s="69"/>
+      <c r="G139" s="70"/>
+      <c r="H139" s="70"/>
+      <c r="I139" s="70"/>
+      <c r="J139" s="70"/>
+      <c r="K139" s="70"/>
+      <c r="L139" s="71"/>
+      <c r="M139" s="71"/>
+      <c r="N139" s="71"/>
+      <c r="O139" s="71"/>
+      <c r="P139" s="70"/>
+      <c r="Q139" s="70"/>
+      <c r="R139" s="70"/>
+      <c r="S139" s="70"/>
+      <c r="T139" s="71"/>
+      <c r="U139" s="71"/>
+      <c r="V139" s="71"/>
+      <c r="W139" s="71"/>
+      <c r="X139" s="70"/>
+      <c r="Y139" s="70"/>
+      <c r="Z139" s="70"/>
+      <c r="AA139" s="71"/>
+      <c r="AB139" s="71"/>
+      <c r="AC139" s="71"/>
+      <c r="AD139" s="71"/>
+      <c r="AE139" s="67"/>
     </row>
     <row r="140" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A140" s="71" t="e">
+      <c r="A140" s="72" t="e">
         <f aca="false" t="array" ref="A140:A144">unique(L1:L120)</f>
         <v>#NAME?</v>
       </c>
-      <c r="B140" s="72"/>
-      <c r="C140" s="73"/>
-      <c r="D140" s="73"/>
-      <c r="E140" s="73"/>
-      <c r="F140" s="74"/>
-      <c r="G140" s="75" t="s">
+      <c r="B140" s="73"/>
+      <c r="C140" s="74"/>
+      <c r="D140" s="74"/>
+      <c r="E140" s="74"/>
+      <c r="F140" s="75"/>
+      <c r="G140" s="76" t="s">
         <v>83</v>
       </c>
-      <c r="H140" s="75" t="s">
+      <c r="H140" s="76" t="s">
         <v>84</v>
       </c>
-      <c r="I140" s="75" t="s">
+      <c r="I140" s="76" t="s">
         <v>85</v>
       </c>
-      <c r="J140" s="75" t="s">
+      <c r="J140" s="76" t="s">
         <v>86</v>
       </c>
-      <c r="K140" s="75" t="s">
+      <c r="K140" s="76" t="s">
         <v>87</v>
       </c>
-      <c r="L140" s="76" t="s">
+      <c r="L140" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="M140" s="76" t="s">
+      <c r="M140" s="77" t="s">
         <v>89</v>
       </c>
-      <c r="N140" s="76" t="s">
+      <c r="N140" s="77" t="s">
         <v>90</v>
       </c>
-      <c r="O140" s="76" t="s">
+      <c r="O140" s="77" t="s">
         <v>91</v>
       </c>
-      <c r="P140" s="75" t="s">
+      <c r="P140" s="76" t="s">
         <v>92</v>
       </c>
-      <c r="Q140" s="75"/>
-      <c r="R140" s="75"/>
-      <c r="S140" s="75"/>
-      <c r="T140" s="76"/>
-      <c r="U140" s="76"/>
-      <c r="V140" s="76"/>
-      <c r="W140" s="76"/>
-      <c r="X140" s="75"/>
-      <c r="Y140" s="75"/>
-      <c r="Z140" s="75"/>
-      <c r="AA140" s="76"/>
-      <c r="AB140" s="76"/>
-      <c r="AC140" s="77"/>
-      <c r="AD140" s="76"/>
-      <c r="AE140" s="22"/>
+      <c r="Q140" s="76"/>
+      <c r="R140" s="76"/>
+      <c r="S140" s="76"/>
+      <c r="T140" s="77"/>
+      <c r="U140" s="77"/>
+      <c r="V140" s="77"/>
+      <c r="W140" s="77"/>
+      <c r="X140" s="76"/>
+      <c r="Y140" s="76"/>
+      <c r="Z140" s="76"/>
+      <c r="AA140" s="77"/>
+      <c r="AB140" s="77"/>
+      <c r="AC140" s="78"/>
+      <c r="AD140" s="77"/>
+      <c r="AE140" s="67"/>
     </row>
     <row r="141" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A141" s="78" t="e">
+      <c r="A141" s="79" t="e">
         <v>#NAME?</v>
       </c>
-      <c r="B141" s="79"/>
-      <c r="C141" s="79"/>
-      <c r="D141" s="79" t="s">
+      <c r="B141" s="80"/>
+      <c r="C141" s="80"/>
+      <c r="D141" s="80" t="s">
         <v>93</v>
       </c>
-      <c r="E141" s="79"/>
-      <c r="F141" s="80"/>
-      <c r="G141" s="81"/>
-      <c r="H141" s="81"/>
-      <c r="I141" s="81"/>
-      <c r="J141" s="81"/>
-      <c r="K141" s="81"/>
-      <c r="L141" s="82"/>
-      <c r="M141" s="82"/>
-      <c r="N141" s="82"/>
-      <c r="O141" s="82"/>
-      <c r="P141" s="81"/>
-      <c r="Q141" s="81"/>
-      <c r="R141" s="81"/>
-      <c r="S141" s="81"/>
-      <c r="T141" s="82"/>
-      <c r="U141" s="82"/>
-      <c r="V141" s="82"/>
-      <c r="W141" s="82"/>
-      <c r="X141" s="81"/>
-      <c r="Y141" s="81"/>
-      <c r="Z141" s="81"/>
-      <c r="AA141" s="82"/>
-      <c r="AB141" s="82"/>
-      <c r="AC141" s="83"/>
-      <c r="AD141" s="82"/>
-      <c r="AE141" s="22"/>
+      <c r="E141" s="80"/>
+      <c r="F141" s="81"/>
+      <c r="G141" s="82"/>
+      <c r="H141" s="82"/>
+      <c r="I141" s="82"/>
+      <c r="J141" s="82"/>
+      <c r="K141" s="82"/>
+      <c r="L141" s="83"/>
+      <c r="M141" s="83"/>
+      <c r="N141" s="83"/>
+      <c r="O141" s="83"/>
+      <c r="P141" s="82"/>
+      <c r="Q141" s="82"/>
+      <c r="R141" s="82"/>
+      <c r="S141" s="82"/>
+      <c r="T141" s="83"/>
+      <c r="U141" s="83"/>
+      <c r="V141" s="83"/>
+      <c r="W141" s="83"/>
+      <c r="X141" s="82"/>
+      <c r="Y141" s="82"/>
+      <c r="Z141" s="82"/>
+      <c r="AA141" s="83"/>
+      <c r="AB141" s="83"/>
+      <c r="AC141" s="84"/>
+      <c r="AD141" s="83"/>
+      <c r="AE141" s="67"/>
     </row>
     <row r="142" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A142" s="78" t="e">
+      <c r="A142" s="79" t="e">
         <v>#NAME?</v>
       </c>
-      <c r="B142" s="79"/>
-      <c r="C142" s="79"/>
-      <c r="D142" s="79"/>
-      <c r="E142" s="79"/>
-      <c r="F142" s="80"/>
-      <c r="G142" s="81"/>
-      <c r="H142" s="81"/>
-      <c r="I142" s="81"/>
-      <c r="J142" s="81"/>
-      <c r="K142" s="81"/>
-      <c r="L142" s="82"/>
-      <c r="M142" s="82"/>
-      <c r="N142" s="82"/>
-      <c r="O142" s="82"/>
-      <c r="P142" s="81"/>
-      <c r="Q142" s="81"/>
-      <c r="R142" s="81"/>
-      <c r="S142" s="81"/>
-      <c r="T142" s="82"/>
-      <c r="U142" s="82"/>
-      <c r="V142" s="82"/>
-      <c r="W142" s="82"/>
-      <c r="X142" s="81"/>
-      <c r="Y142" s="81"/>
-      <c r="Z142" s="81"/>
-      <c r="AA142" s="82"/>
-      <c r="AB142" s="82"/>
-      <c r="AC142" s="83"/>
-      <c r="AD142" s="82"/>
-      <c r="AE142" s="22"/>
+      <c r="B142" s="80"/>
+      <c r="C142" s="80"/>
+      <c r="D142" s="80"/>
+      <c r="E142" s="80"/>
+      <c r="F142" s="81"/>
+      <c r="G142" s="82"/>
+      <c r="H142" s="82"/>
+      <c r="I142" s="82"/>
+      <c r="J142" s="82"/>
+      <c r="K142" s="82"/>
+      <c r="L142" s="83"/>
+      <c r="M142" s="83"/>
+      <c r="N142" s="83"/>
+      <c r="O142" s="83"/>
+      <c r="P142" s="82"/>
+      <c r="Q142" s="82"/>
+      <c r="R142" s="82"/>
+      <c r="S142" s="82"/>
+      <c r="T142" s="83"/>
+      <c r="U142" s="83"/>
+      <c r="V142" s="83"/>
+      <c r="W142" s="83"/>
+      <c r="X142" s="82"/>
+      <c r="Y142" s="82"/>
+      <c r="Z142" s="82"/>
+      <c r="AA142" s="83"/>
+      <c r="AB142" s="83"/>
+      <c r="AC142" s="84"/>
+      <c r="AD142" s="83"/>
+      <c r="AE142" s="67"/>
     </row>
     <row r="143" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A143" s="78" t="e">
+      <c r="A143" s="79" t="e">
         <v>#NAME?</v>
       </c>
-      <c r="B143" s="79"/>
-      <c r="C143" s="79"/>
-      <c r="D143" s="79"/>
-      <c r="E143" s="79"/>
-      <c r="F143" s="80"/>
-      <c r="G143" s="81"/>
-      <c r="H143" s="81"/>
-      <c r="I143" s="81"/>
-      <c r="J143" s="81"/>
-      <c r="K143" s="81"/>
-      <c r="L143" s="82"/>
-      <c r="M143" s="82"/>
-      <c r="N143" s="82"/>
-      <c r="O143" s="82"/>
-      <c r="P143" s="81"/>
-      <c r="Q143" s="81"/>
-      <c r="R143" s="81"/>
-      <c r="S143" s="81"/>
-      <c r="T143" s="82"/>
-      <c r="U143" s="82"/>
-      <c r="V143" s="82"/>
-      <c r="W143" s="82"/>
-      <c r="X143" s="81"/>
-      <c r="Y143" s="81"/>
-      <c r="Z143" s="81"/>
-      <c r="AA143" s="82"/>
-      <c r="AB143" s="82"/>
-      <c r="AC143" s="83"/>
-      <c r="AD143" s="82"/>
-      <c r="AE143" s="22"/>
+      <c r="B143" s="80"/>
+      <c r="C143" s="80"/>
+      <c r="D143" s="80"/>
+      <c r="E143" s="80"/>
+      <c r="F143" s="81"/>
+      <c r="G143" s="82"/>
+      <c r="H143" s="82"/>
+      <c r="I143" s="82"/>
+      <c r="J143" s="82"/>
+      <c r="K143" s="82"/>
+      <c r="L143" s="83"/>
+      <c r="M143" s="83"/>
+      <c r="N143" s="83"/>
+      <c r="O143" s="83"/>
+      <c r="P143" s="82"/>
+      <c r="Q143" s="82"/>
+      <c r="R143" s="82"/>
+      <c r="S143" s="82"/>
+      <c r="T143" s="83"/>
+      <c r="U143" s="83"/>
+      <c r="V143" s="83"/>
+      <c r="W143" s="83"/>
+      <c r="X143" s="82"/>
+      <c r="Y143" s="82"/>
+      <c r="Z143" s="82"/>
+      <c r="AA143" s="83"/>
+      <c r="AB143" s="83"/>
+      <c r="AC143" s="84"/>
+      <c r="AD143" s="83"/>
+      <c r="AE143" s="67"/>
     </row>
     <row r="144" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A144" s="78" t="e">
+      <c r="A144" s="79" t="e">
         <v>#NAME?</v>
       </c>
-      <c r="B144" s="79"/>
-      <c r="C144" s="79"/>
-      <c r="D144" s="79"/>
-      <c r="E144" s="79"/>
-      <c r="F144" s="80"/>
-      <c r="G144" s="81"/>
-      <c r="H144" s="81"/>
-      <c r="I144" s="81"/>
-      <c r="J144" s="81"/>
-      <c r="K144" s="81"/>
-      <c r="L144" s="82"/>
-      <c r="M144" s="82"/>
-      <c r="N144" s="82"/>
-      <c r="O144" s="82"/>
-      <c r="P144" s="81"/>
-      <c r="Q144" s="81"/>
-      <c r="R144" s="81"/>
-      <c r="S144" s="81"/>
-      <c r="T144" s="82"/>
-      <c r="U144" s="82"/>
-      <c r="V144" s="82"/>
-      <c r="W144" s="82"/>
-      <c r="X144" s="81"/>
-      <c r="Y144" s="81"/>
-      <c r="Z144" s="81"/>
-      <c r="AA144" s="82"/>
-      <c r="AB144" s="82"/>
-      <c r="AC144" s="83"/>
-      <c r="AD144" s="82"/>
-      <c r="AE144" s="22"/>
+      <c r="B144" s="80"/>
+      <c r="C144" s="80"/>
+      <c r="D144" s="80"/>
+      <c r="E144" s="80"/>
+      <c r="F144" s="81"/>
+      <c r="G144" s="82"/>
+      <c r="H144" s="82"/>
+      <c r="I144" s="82"/>
+      <c r="J144" s="82"/>
+      <c r="K144" s="82"/>
+      <c r="L144" s="83"/>
+      <c r="M144" s="83"/>
+      <c r="N144" s="83"/>
+      <c r="O144" s="83"/>
+      <c r="P144" s="82"/>
+      <c r="Q144" s="82"/>
+      <c r="R144" s="82"/>
+      <c r="S144" s="82"/>
+      <c r="T144" s="83"/>
+      <c r="U144" s="83"/>
+      <c r="V144" s="83"/>
+      <c r="W144" s="83"/>
+      <c r="X144" s="82"/>
+      <c r="Y144" s="82"/>
+      <c r="Z144" s="82"/>
+      <c r="AA144" s="83"/>
+      <c r="AB144" s="83"/>
+      <c r="AC144" s="84"/>
+      <c r="AD144" s="83"/>
+      <c r="AE144" s="67"/>
     </row>
     <row r="145" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A145" s="78"/>
-      <c r="B145" s="79"/>
-      <c r="C145" s="79"/>
-      <c r="D145" s="79"/>
-      <c r="E145" s="79"/>
-      <c r="F145" s="80"/>
-      <c r="G145" s="81"/>
-      <c r="H145" s="81"/>
-      <c r="I145" s="81"/>
-      <c r="J145" s="81"/>
-      <c r="K145" s="81"/>
-      <c r="L145" s="82"/>
-      <c r="M145" s="82"/>
-      <c r="N145" s="82"/>
-      <c r="O145" s="82"/>
-      <c r="P145" s="81"/>
-      <c r="Q145" s="81"/>
-      <c r="R145" s="81"/>
-      <c r="S145" s="81"/>
-      <c r="T145" s="82"/>
-      <c r="U145" s="82"/>
-      <c r="V145" s="82"/>
-      <c r="W145" s="82"/>
-      <c r="X145" s="81"/>
-      <c r="Y145" s="81"/>
-      <c r="Z145" s="81"/>
-      <c r="AA145" s="82"/>
-      <c r="AB145" s="82"/>
-      <c r="AC145" s="83"/>
-      <c r="AD145" s="82"/>
-      <c r="AE145" s="22"/>
+      <c r="A145" s="79"/>
+      <c r="B145" s="80"/>
+      <c r="C145" s="80"/>
+      <c r="D145" s="80"/>
+      <c r="E145" s="80"/>
+      <c r="F145" s="81"/>
+      <c r="G145" s="82"/>
+      <c r="H145" s="82"/>
+      <c r="I145" s="82"/>
+      <c r="J145" s="82"/>
+      <c r="K145" s="82"/>
+      <c r="L145" s="83"/>
+      <c r="M145" s="83"/>
+      <c r="N145" s="83"/>
+      <c r="O145" s="83"/>
+      <c r="P145" s="82"/>
+      <c r="Q145" s="82"/>
+      <c r="R145" s="82"/>
+      <c r="S145" s="82"/>
+      <c r="T145" s="83"/>
+      <c r="U145" s="83"/>
+      <c r="V145" s="83"/>
+      <c r="W145" s="83"/>
+      <c r="X145" s="82"/>
+      <c r="Y145" s="82"/>
+      <c r="Z145" s="82"/>
+      <c r="AA145" s="83"/>
+      <c r="AB145" s="83"/>
+      <c r="AC145" s="84"/>
+      <c r="AD145" s="83"/>
+      <c r="AE145" s="67"/>
     </row>
     <row r="146" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A146" s="78"/>
-      <c r="B146" s="79"/>
-      <c r="C146" s="79"/>
-      <c r="D146" s="79"/>
-      <c r="E146" s="79"/>
-      <c r="F146" s="80"/>
-      <c r="G146" s="81"/>
-      <c r="H146" s="81"/>
-      <c r="I146" s="81"/>
-      <c r="J146" s="81"/>
-      <c r="K146" s="81"/>
-      <c r="L146" s="82"/>
-      <c r="M146" s="82"/>
-      <c r="N146" s="82"/>
-      <c r="O146" s="82"/>
-      <c r="P146" s="81"/>
-      <c r="Q146" s="81"/>
-      <c r="R146" s="81"/>
-      <c r="S146" s="81"/>
-      <c r="T146" s="82"/>
-      <c r="U146" s="82"/>
-      <c r="V146" s="82"/>
-      <c r="W146" s="82"/>
-      <c r="X146" s="81"/>
-      <c r="Y146" s="81"/>
-      <c r="Z146" s="81"/>
-      <c r="AA146" s="82"/>
-      <c r="AB146" s="82"/>
-      <c r="AC146" s="83"/>
-      <c r="AD146" s="82"/>
-      <c r="AE146" s="22"/>
+      <c r="A146" s="79"/>
+      <c r="B146" s="80"/>
+      <c r="C146" s="80"/>
+      <c r="D146" s="80"/>
+      <c r="E146" s="80"/>
+      <c r="F146" s="81"/>
+      <c r="G146" s="82"/>
+      <c r="H146" s="82"/>
+      <c r="I146" s="82"/>
+      <c r="J146" s="82"/>
+      <c r="K146" s="82"/>
+      <c r="L146" s="83"/>
+      <c r="M146" s="83"/>
+      <c r="N146" s="83"/>
+      <c r="O146" s="83"/>
+      <c r="P146" s="82"/>
+      <c r="Q146" s="82"/>
+      <c r="R146" s="82"/>
+      <c r="S146" s="82"/>
+      <c r="T146" s="83"/>
+      <c r="U146" s="83"/>
+      <c r="V146" s="83"/>
+      <c r="W146" s="83"/>
+      <c r="X146" s="82"/>
+      <c r="Y146" s="82"/>
+      <c r="Z146" s="82"/>
+      <c r="AA146" s="83"/>
+      <c r="AB146" s="83"/>
+      <c r="AC146" s="84"/>
+      <c r="AD146" s="83"/>
+      <c r="AE146" s="67"/>
     </row>
     <row r="147" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A147" s="78"/>
-      <c r="B147" s="79"/>
-      <c r="C147" s="79"/>
-      <c r="D147" s="79"/>
-      <c r="E147" s="79"/>
-      <c r="F147" s="80"/>
-      <c r="G147" s="81"/>
-      <c r="H147" s="81"/>
-      <c r="I147" s="81"/>
-      <c r="J147" s="81"/>
-      <c r="K147" s="81"/>
-      <c r="L147" s="82"/>
-      <c r="M147" s="82"/>
-      <c r="N147" s="82"/>
-      <c r="O147" s="82"/>
-      <c r="P147" s="81"/>
-      <c r="Q147" s="81"/>
-      <c r="R147" s="81"/>
-      <c r="S147" s="81"/>
-      <c r="T147" s="82"/>
-      <c r="U147" s="82"/>
-      <c r="V147" s="82"/>
-      <c r="W147" s="82"/>
-      <c r="X147" s="81"/>
-      <c r="Y147" s="81"/>
-      <c r="Z147" s="81"/>
-      <c r="AA147" s="82"/>
-      <c r="AB147" s="82"/>
-      <c r="AC147" s="83"/>
-      <c r="AD147" s="82"/>
-      <c r="AE147" s="22"/>
+      <c r="A147" s="79"/>
+      <c r="B147" s="80"/>
+      <c r="C147" s="80"/>
+      <c r="D147" s="80"/>
+      <c r="E147" s="80"/>
+      <c r="F147" s="81"/>
+      <c r="G147" s="82"/>
+      <c r="H147" s="82"/>
+      <c r="I147" s="82"/>
+      <c r="J147" s="82"/>
+      <c r="K147" s="82"/>
+      <c r="L147" s="83"/>
+      <c r="M147" s="83"/>
+      <c r="N147" s="83"/>
+      <c r="O147" s="83"/>
+      <c r="P147" s="82"/>
+      <c r="Q147" s="82"/>
+      <c r="R147" s="82"/>
+      <c r="S147" s="82"/>
+      <c r="T147" s="83"/>
+      <c r="U147" s="83"/>
+      <c r="V147" s="83"/>
+      <c r="W147" s="83"/>
+      <c r="X147" s="82"/>
+      <c r="Y147" s="82"/>
+      <c r="Z147" s="82"/>
+      <c r="AA147" s="83"/>
+      <c r="AB147" s="83"/>
+      <c r="AC147" s="84"/>
+      <c r="AD147" s="83"/>
+      <c r="AE147" s="67"/>
     </row>
     <row r="148" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A148" s="78"/>
-      <c r="B148" s="79"/>
-      <c r="C148" s="79"/>
-      <c r="D148" s="79"/>
-      <c r="E148" s="79"/>
-      <c r="F148" s="80"/>
-      <c r="G148" s="81"/>
-      <c r="H148" s="81"/>
-      <c r="I148" s="81"/>
-      <c r="J148" s="81"/>
-      <c r="K148" s="81"/>
-      <c r="L148" s="82"/>
-      <c r="M148" s="82"/>
-      <c r="N148" s="82"/>
-      <c r="O148" s="82"/>
-      <c r="P148" s="81"/>
-      <c r="Q148" s="81"/>
-      <c r="R148" s="81"/>
-      <c r="S148" s="81"/>
-      <c r="T148" s="82"/>
-      <c r="U148" s="82"/>
-      <c r="V148" s="82"/>
-      <c r="W148" s="82"/>
-      <c r="X148" s="81"/>
-      <c r="Y148" s="81"/>
-      <c r="Z148" s="81"/>
-      <c r="AA148" s="82"/>
-      <c r="AB148" s="82"/>
-      <c r="AC148" s="83"/>
-      <c r="AD148" s="82"/>
-      <c r="AE148" s="22"/>
+      <c r="A148" s="79"/>
+      <c r="B148" s="80"/>
+      <c r="C148" s="80"/>
+      <c r="D148" s="80"/>
+      <c r="E148" s="80"/>
+      <c r="F148" s="81"/>
+      <c r="G148" s="82"/>
+      <c r="H148" s="82"/>
+      <c r="I148" s="82"/>
+      <c r="J148" s="82"/>
+      <c r="K148" s="82"/>
+      <c r="L148" s="83"/>
+      <c r="M148" s="83"/>
+      <c r="N148" s="83"/>
+      <c r="O148" s="83"/>
+      <c r="P148" s="82"/>
+      <c r="Q148" s="82"/>
+      <c r="R148" s="82"/>
+      <c r="S148" s="82"/>
+      <c r="T148" s="83"/>
+      <c r="U148" s="83"/>
+      <c r="V148" s="83"/>
+      <c r="W148" s="83"/>
+      <c r="X148" s="82"/>
+      <c r="Y148" s="82"/>
+      <c r="Z148" s="82"/>
+      <c r="AA148" s="83"/>
+      <c r="AB148" s="83"/>
+      <c r="AC148" s="84"/>
+      <c r="AD148" s="83"/>
+      <c r="AE148" s="67"/>
     </row>
     <row r="149" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A149" s="78"/>
-      <c r="B149" s="79"/>
-      <c r="C149" s="79"/>
-      <c r="D149" s="79"/>
-      <c r="E149" s="79"/>
-      <c r="F149" s="80"/>
-      <c r="G149" s="81"/>
-      <c r="H149" s="81"/>
-      <c r="I149" s="81"/>
-      <c r="J149" s="81"/>
-      <c r="K149" s="81"/>
-      <c r="L149" s="82"/>
-      <c r="M149" s="82"/>
-      <c r="N149" s="82"/>
-      <c r="O149" s="82"/>
-      <c r="P149" s="81"/>
-      <c r="Q149" s="81"/>
-      <c r="R149" s="81"/>
-      <c r="S149" s="81"/>
-      <c r="T149" s="82"/>
-      <c r="U149" s="82"/>
-      <c r="V149" s="82"/>
-      <c r="W149" s="82"/>
-      <c r="X149" s="81"/>
-      <c r="Y149" s="81"/>
-      <c r="Z149" s="81"/>
-      <c r="AA149" s="82"/>
-      <c r="AB149" s="82"/>
-      <c r="AC149" s="83"/>
-      <c r="AD149" s="82"/>
-      <c r="AE149" s="22"/>
+      <c r="A149" s="79"/>
+      <c r="B149" s="80"/>
+      <c r="C149" s="80"/>
+      <c r="D149" s="80"/>
+      <c r="E149" s="80"/>
+      <c r="F149" s="81"/>
+      <c r="G149" s="82"/>
+      <c r="H149" s="82"/>
+      <c r="I149" s="82"/>
+      <c r="J149" s="82"/>
+      <c r="K149" s="82"/>
+      <c r="L149" s="83"/>
+      <c r="M149" s="83"/>
+      <c r="N149" s="83"/>
+      <c r="O149" s="83"/>
+      <c r="P149" s="82"/>
+      <c r="Q149" s="82"/>
+      <c r="R149" s="82"/>
+      <c r="S149" s="82"/>
+      <c r="T149" s="83"/>
+      <c r="U149" s="83"/>
+      <c r="V149" s="83"/>
+      <c r="W149" s="83"/>
+      <c r="X149" s="82"/>
+      <c r="Y149" s="82"/>
+      <c r="Z149" s="82"/>
+      <c r="AA149" s="83"/>
+      <c r="AB149" s="83"/>
+      <c r="AC149" s="84"/>
+      <c r="AD149" s="83"/>
+      <c r="AE149" s="67"/>
     </row>
     <row r="150" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A150" s="78"/>
-      <c r="B150" s="79"/>
-      <c r="C150" s="79"/>
-      <c r="D150" s="79"/>
-      <c r="E150" s="79"/>
-      <c r="F150" s="80"/>
-      <c r="G150" s="81"/>
-      <c r="H150" s="81"/>
-      <c r="I150" s="81"/>
-      <c r="J150" s="81"/>
-      <c r="K150" s="81"/>
-      <c r="L150" s="82"/>
-      <c r="M150" s="82"/>
-      <c r="N150" s="82"/>
-      <c r="O150" s="82"/>
-      <c r="P150" s="81"/>
-      <c r="Q150" s="81"/>
-      <c r="R150" s="81"/>
-      <c r="S150" s="81"/>
-      <c r="T150" s="82"/>
-      <c r="U150" s="82"/>
-      <c r="V150" s="82"/>
-      <c r="W150" s="82"/>
-      <c r="X150" s="81"/>
-      <c r="Y150" s="81"/>
-      <c r="Z150" s="81"/>
-      <c r="AA150" s="82"/>
-      <c r="AB150" s="82"/>
-      <c r="AC150" s="83"/>
-      <c r="AD150" s="82"/>
-      <c r="AE150" s="22"/>
+      <c r="A150" s="79"/>
+      <c r="B150" s="80"/>
+      <c r="C150" s="80"/>
+      <c r="D150" s="80"/>
+      <c r="E150" s="80"/>
+      <c r="F150" s="81"/>
+      <c r="G150" s="82"/>
+      <c r="H150" s="82"/>
+      <c r="I150" s="82"/>
+      <c r="J150" s="82"/>
+      <c r="K150" s="82"/>
+      <c r="L150" s="83"/>
+      <c r="M150" s="83"/>
+      <c r="N150" s="83"/>
+      <c r="O150" s="83"/>
+      <c r="P150" s="82"/>
+      <c r="Q150" s="82"/>
+      <c r="R150" s="82"/>
+      <c r="S150" s="82"/>
+      <c r="T150" s="83"/>
+      <c r="U150" s="83"/>
+      <c r="V150" s="83"/>
+      <c r="W150" s="83"/>
+      <c r="X150" s="82"/>
+      <c r="Y150" s="82"/>
+      <c r="Z150" s="82"/>
+      <c r="AA150" s="83"/>
+      <c r="AB150" s="83"/>
+      <c r="AC150" s="84"/>
+      <c r="AD150" s="83"/>
+      <c r="AE150" s="67"/>
     </row>
     <row r="151" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A151" s="78"/>
-      <c r="B151" s="79"/>
-      <c r="C151" s="79"/>
-      <c r="D151" s="79"/>
-      <c r="E151" s="79"/>
-      <c r="F151" s="80"/>
-      <c r="G151" s="81"/>
-      <c r="H151" s="81"/>
-      <c r="I151" s="81"/>
-      <c r="J151" s="81"/>
-      <c r="K151" s="81"/>
-      <c r="L151" s="82"/>
-      <c r="M151" s="82"/>
-      <c r="N151" s="82"/>
-      <c r="O151" s="82"/>
-      <c r="P151" s="81"/>
-      <c r="Q151" s="81"/>
-      <c r="R151" s="81"/>
-      <c r="S151" s="81"/>
-      <c r="T151" s="82"/>
-      <c r="U151" s="82"/>
-      <c r="V151" s="82"/>
-      <c r="W151" s="82"/>
-      <c r="X151" s="81"/>
-      <c r="Y151" s="81"/>
-      <c r="Z151" s="81"/>
-      <c r="AA151" s="82"/>
-      <c r="AB151" s="82"/>
-      <c r="AC151" s="83"/>
-      <c r="AD151" s="82"/>
-      <c r="AE151" s="22"/>
+      <c r="A151" s="79"/>
+      <c r="B151" s="80"/>
+      <c r="C151" s="80"/>
+      <c r="D151" s="80"/>
+      <c r="E151" s="80"/>
+      <c r="F151" s="81"/>
+      <c r="G151" s="82"/>
+      <c r="H151" s="82"/>
+      <c r="I151" s="82"/>
+      <c r="J151" s="82"/>
+      <c r="K151" s="82"/>
+      <c r="L151" s="83"/>
+      <c r="M151" s="83"/>
+      <c r="N151" s="83"/>
+      <c r="O151" s="83"/>
+      <c r="P151" s="82"/>
+      <c r="Q151" s="82"/>
+      <c r="R151" s="82"/>
+      <c r="S151" s="82"/>
+      <c r="T151" s="83"/>
+      <c r="U151" s="83"/>
+      <c r="V151" s="83"/>
+      <c r="W151" s="83"/>
+      <c r="X151" s="82"/>
+      <c r="Y151" s="82"/>
+      <c r="Z151" s="82"/>
+      <c r="AA151" s="83"/>
+      <c r="AB151" s="83"/>
+      <c r="AC151" s="84"/>
+      <c r="AD151" s="83"/>
+      <c r="AE151" s="67"/>
     </row>
     <row r="152" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A152" s="78"/>
-      <c r="B152" s="79"/>
-      <c r="C152" s="79"/>
-      <c r="D152" s="79"/>
-      <c r="E152" s="79"/>
-      <c r="F152" s="80"/>
-      <c r="G152" s="81"/>
-      <c r="H152" s="81"/>
-      <c r="I152" s="81"/>
-      <c r="J152" s="81"/>
-      <c r="K152" s="81"/>
-      <c r="L152" s="82"/>
-      <c r="M152" s="82"/>
-      <c r="N152" s="82"/>
-      <c r="O152" s="82"/>
-      <c r="P152" s="81"/>
-      <c r="Q152" s="81"/>
-      <c r="R152" s="81"/>
-      <c r="S152" s="81"/>
-      <c r="T152" s="82"/>
-      <c r="U152" s="82"/>
-      <c r="V152" s="82"/>
-      <c r="W152" s="82"/>
-      <c r="X152" s="81"/>
-      <c r="Y152" s="81"/>
-      <c r="Z152" s="81"/>
-      <c r="AA152" s="82"/>
-      <c r="AB152" s="82"/>
-      <c r="AC152" s="83"/>
-      <c r="AD152" s="82"/>
-      <c r="AE152" s="22"/>
+      <c r="A152" s="79"/>
+      <c r="B152" s="80"/>
+      <c r="C152" s="80"/>
+      <c r="D152" s="80"/>
+      <c r="E152" s="80"/>
+      <c r="F152" s="81"/>
+      <c r="G152" s="82"/>
+      <c r="H152" s="82"/>
+      <c r="I152" s="82"/>
+      <c r="J152" s="82"/>
+      <c r="K152" s="82"/>
+      <c r="L152" s="83"/>
+      <c r="M152" s="83"/>
+      <c r="N152" s="83"/>
+      <c r="O152" s="83"/>
+      <c r="P152" s="82"/>
+      <c r="Q152" s="82"/>
+      <c r="R152" s="82"/>
+      <c r="S152" s="82"/>
+      <c r="T152" s="83"/>
+      <c r="U152" s="83"/>
+      <c r="V152" s="83"/>
+      <c r="W152" s="83"/>
+      <c r="X152" s="82"/>
+      <c r="Y152" s="82"/>
+      <c r="Z152" s="82"/>
+      <c r="AA152" s="83"/>
+      <c r="AB152" s="83"/>
+      <c r="AC152" s="84"/>
+      <c r="AD152" s="83"/>
+      <c r="AE152" s="67"/>
     </row>
     <row r="153" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A153" s="78"/>
-      <c r="B153" s="79"/>
-      <c r="C153" s="79"/>
-      <c r="D153" s="79"/>
-      <c r="E153" s="79"/>
-      <c r="F153" s="80"/>
-      <c r="G153" s="81"/>
-      <c r="H153" s="81"/>
-      <c r="I153" s="81"/>
-      <c r="J153" s="81"/>
-      <c r="K153" s="81"/>
-      <c r="L153" s="82"/>
-      <c r="M153" s="82"/>
-      <c r="N153" s="82"/>
-      <c r="O153" s="82"/>
-      <c r="P153" s="81"/>
-      <c r="Q153" s="81"/>
-      <c r="R153" s="81"/>
-      <c r="S153" s="81"/>
-      <c r="T153" s="82"/>
-      <c r="U153" s="82"/>
-      <c r="V153" s="82"/>
-      <c r="W153" s="82"/>
-      <c r="X153" s="81"/>
-      <c r="Y153" s="81"/>
-      <c r="Z153" s="81"/>
-      <c r="AA153" s="82"/>
-      <c r="AB153" s="82"/>
-      <c r="AC153" s="83"/>
-      <c r="AD153" s="82"/>
-      <c r="AE153" s="22"/>
+      <c r="A153" s="79"/>
+      <c r="B153" s="80"/>
+      <c r="C153" s="80"/>
+      <c r="D153" s="80"/>
+      <c r="E153" s="80"/>
+      <c r="F153" s="81"/>
+      <c r="G153" s="82"/>
+      <c r="H153" s="82"/>
+      <c r="I153" s="82"/>
+      <c r="J153" s="82"/>
+      <c r="K153" s="82"/>
+      <c r="L153" s="83"/>
+      <c r="M153" s="83"/>
+      <c r="N153" s="83"/>
+      <c r="O153" s="83"/>
+      <c r="P153" s="82"/>
+      <c r="Q153" s="82"/>
+      <c r="R153" s="82"/>
+      <c r="S153" s="82"/>
+      <c r="T153" s="83"/>
+      <c r="U153" s="83"/>
+      <c r="V153" s="83"/>
+      <c r="W153" s="83"/>
+      <c r="X153" s="82"/>
+      <c r="Y153" s="82"/>
+      <c r="Z153" s="82"/>
+      <c r="AA153" s="83"/>
+      <c r="AB153" s="83"/>
+      <c r="AC153" s="84"/>
+      <c r="AD153" s="83"/>
+      <c r="AE153" s="67"/>
     </row>
     <row r="154" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A154" s="78"/>
-      <c r="B154" s="79"/>
-      <c r="C154" s="79"/>
-      <c r="D154" s="79"/>
-      <c r="E154" s="79"/>
-      <c r="F154" s="80"/>
-      <c r="G154" s="81"/>
-      <c r="H154" s="81"/>
-      <c r="I154" s="81"/>
-      <c r="J154" s="81"/>
-      <c r="K154" s="81"/>
-      <c r="L154" s="82"/>
-      <c r="M154" s="82"/>
-      <c r="N154" s="82"/>
-      <c r="O154" s="82"/>
-      <c r="P154" s="81"/>
-      <c r="Q154" s="81"/>
-      <c r="R154" s="81"/>
-      <c r="S154" s="81"/>
-      <c r="T154" s="82"/>
-      <c r="U154" s="82"/>
-      <c r="V154" s="82"/>
-      <c r="W154" s="82"/>
-      <c r="X154" s="81"/>
-      <c r="Y154" s="81"/>
-      <c r="Z154" s="81"/>
-      <c r="AA154" s="82"/>
-      <c r="AB154" s="82"/>
-      <c r="AC154" s="83"/>
-      <c r="AD154" s="82"/>
-      <c r="AE154" s="22"/>
+      <c r="A154" s="79"/>
+      <c r="B154" s="80"/>
+      <c r="C154" s="80"/>
+      <c r="D154" s="80"/>
+      <c r="E154" s="80"/>
+      <c r="F154" s="81"/>
+      <c r="G154" s="82"/>
+      <c r="H154" s="82"/>
+      <c r="I154" s="82"/>
+      <c r="J154" s="82"/>
+      <c r="K154" s="82"/>
+      <c r="L154" s="83"/>
+      <c r="M154" s="83"/>
+      <c r="N154" s="83"/>
+      <c r="O154" s="83"/>
+      <c r="P154" s="82"/>
+      <c r="Q154" s="82"/>
+      <c r="R154" s="82"/>
+      <c r="S154" s="82"/>
+      <c r="T154" s="83"/>
+      <c r="U154" s="83"/>
+      <c r="V154" s="83"/>
+      <c r="W154" s="83"/>
+      <c r="X154" s="82"/>
+      <c r="Y154" s="82"/>
+      <c r="Z154" s="82"/>
+      <c r="AA154" s="83"/>
+      <c r="AB154" s="83"/>
+      <c r="AC154" s="84"/>
+      <c r="AD154" s="83"/>
+      <c r="AE154" s="67"/>
     </row>
     <row r="155" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A155" s="78"/>
-      <c r="B155" s="79"/>
-      <c r="C155" s="79"/>
-      <c r="D155" s="79"/>
-      <c r="E155" s="79"/>
-      <c r="F155" s="80"/>
-      <c r="G155" s="81"/>
-      <c r="H155" s="81"/>
-      <c r="I155" s="81"/>
-      <c r="J155" s="81"/>
-      <c r="K155" s="81"/>
-      <c r="L155" s="82"/>
-      <c r="M155" s="82"/>
-      <c r="N155" s="82"/>
-      <c r="O155" s="82"/>
-      <c r="P155" s="81"/>
-      <c r="Q155" s="81"/>
-      <c r="R155" s="81"/>
-      <c r="S155" s="81"/>
-      <c r="T155" s="82"/>
-      <c r="U155" s="82"/>
-      <c r="V155" s="82"/>
-      <c r="W155" s="82"/>
-      <c r="X155" s="81"/>
-      <c r="Y155" s="81"/>
-      <c r="Z155" s="81"/>
-      <c r="AA155" s="82"/>
-      <c r="AB155" s="82"/>
-      <c r="AC155" s="83"/>
-      <c r="AD155" s="82"/>
-      <c r="AE155" s="22"/>
+      <c r="A155" s="79"/>
+      <c r="B155" s="80"/>
+      <c r="C155" s="80"/>
+      <c r="D155" s="80"/>
+      <c r="E155" s="80"/>
+      <c r="F155" s="81"/>
+      <c r="G155" s="82"/>
+      <c r="H155" s="82"/>
+      <c r="I155" s="82"/>
+      <c r="J155" s="82"/>
+      <c r="K155" s="82"/>
+      <c r="L155" s="83"/>
+      <c r="M155" s="83"/>
+      <c r="N155" s="83"/>
+      <c r="O155" s="83"/>
+      <c r="P155" s="82"/>
+      <c r="Q155" s="82"/>
+      <c r="R155" s="82"/>
+      <c r="S155" s="82"/>
+      <c r="T155" s="83"/>
+      <c r="U155" s="83"/>
+      <c r="V155" s="83"/>
+      <c r="W155" s="83"/>
+      <c r="X155" s="82"/>
+      <c r="Y155" s="82"/>
+      <c r="Z155" s="82"/>
+      <c r="AA155" s="83"/>
+      <c r="AB155" s="83"/>
+      <c r="AC155" s="84"/>
+      <c r="AD155" s="83"/>
+      <c r="AE155" s="67"/>
     </row>
     <row r="156" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A156" s="78"/>
-      <c r="B156" s="79"/>
-      <c r="C156" s="79"/>
-      <c r="D156" s="79"/>
-      <c r="E156" s="79"/>
-      <c r="F156" s="80"/>
-      <c r="G156" s="81"/>
-      <c r="H156" s="81"/>
-      <c r="I156" s="81"/>
-      <c r="J156" s="81"/>
-      <c r="K156" s="81"/>
-      <c r="L156" s="82"/>
-      <c r="M156" s="82"/>
-      <c r="N156" s="82"/>
-      <c r="O156" s="82"/>
-      <c r="P156" s="81"/>
-      <c r="Q156" s="81"/>
-      <c r="R156" s="81"/>
-      <c r="S156" s="81"/>
-      <c r="T156" s="82"/>
-      <c r="U156" s="82"/>
-      <c r="V156" s="82"/>
-      <c r="W156" s="82"/>
-      <c r="X156" s="81"/>
-      <c r="Y156" s="81"/>
-      <c r="Z156" s="81"/>
-      <c r="AA156" s="82"/>
-      <c r="AB156" s="82"/>
-      <c r="AC156" s="83"/>
-      <c r="AD156" s="82"/>
-      <c r="AE156" s="22"/>
+      <c r="A156" s="79"/>
+      <c r="B156" s="80"/>
+      <c r="C156" s="80"/>
+      <c r="D156" s="80"/>
+      <c r="E156" s="80"/>
+      <c r="F156" s="81"/>
+      <c r="G156" s="82"/>
+      <c r="H156" s="82"/>
+      <c r="I156" s="82"/>
+      <c r="J156" s="82"/>
+      <c r="K156" s="82"/>
+      <c r="L156" s="83"/>
+      <c r="M156" s="83"/>
+      <c r="N156" s="83"/>
+      <c r="O156" s="83"/>
+      <c r="P156" s="82"/>
+      <c r="Q156" s="82"/>
+      <c r="R156" s="82"/>
+      <c r="S156" s="82"/>
+      <c r="T156" s="83"/>
+      <c r="U156" s="83"/>
+      <c r="V156" s="83"/>
+      <c r="W156" s="83"/>
+      <c r="X156" s="82"/>
+      <c r="Y156" s="82"/>
+      <c r="Z156" s="82"/>
+      <c r="AA156" s="83"/>
+      <c r="AB156" s="83"/>
+      <c r="AC156" s="84"/>
+      <c r="AD156" s="83"/>
+      <c r="AE156" s="67"/>
     </row>
     <row r="157" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A157" s="78"/>
-      <c r="B157" s="79"/>
-      <c r="C157" s="79"/>
-      <c r="D157" s="79"/>
-      <c r="E157" s="79"/>
-      <c r="F157" s="80"/>
-      <c r="G157" s="81"/>
-      <c r="H157" s="81"/>
-      <c r="I157" s="81"/>
-      <c r="J157" s="81"/>
-      <c r="K157" s="81"/>
-      <c r="L157" s="82"/>
-      <c r="M157" s="82"/>
-      <c r="N157" s="82"/>
-      <c r="O157" s="82"/>
-      <c r="P157" s="81"/>
-      <c r="Q157" s="81"/>
-      <c r="R157" s="81"/>
-      <c r="S157" s="81"/>
-      <c r="T157" s="82"/>
-      <c r="U157" s="82"/>
-      <c r="V157" s="82"/>
-      <c r="W157" s="82"/>
-      <c r="X157" s="81"/>
-      <c r="Y157" s="81"/>
-      <c r="Z157" s="81"/>
-      <c r="AA157" s="82"/>
-      <c r="AB157" s="82"/>
-      <c r="AC157" s="83"/>
-      <c r="AD157" s="82"/>
-      <c r="AE157" s="22"/>
+      <c r="A157" s="79"/>
+      <c r="B157" s="80"/>
+      <c r="C157" s="80"/>
+      <c r="D157" s="80"/>
+      <c r="E157" s="80"/>
+      <c r="F157" s="81"/>
+      <c r="G157" s="82"/>
+      <c r="H157" s="82"/>
+      <c r="I157" s="82"/>
+      <c r="J157" s="82"/>
+      <c r="K157" s="82"/>
+      <c r="L157" s="83"/>
+      <c r="M157" s="83"/>
+      <c r="N157" s="83"/>
+      <c r="O157" s="83"/>
+      <c r="P157" s="82"/>
+      <c r="Q157" s="82"/>
+      <c r="R157" s="82"/>
+      <c r="S157" s="82"/>
+      <c r="T157" s="83"/>
+      <c r="U157" s="83"/>
+      <c r="V157" s="83"/>
+      <c r="W157" s="83"/>
+      <c r="X157" s="82"/>
+      <c r="Y157" s="82"/>
+      <c r="Z157" s="82"/>
+      <c r="AA157" s="83"/>
+      <c r="AB157" s="83"/>
+      <c r="AC157" s="84"/>
+      <c r="AD157" s="83"/>
+      <c r="AE157" s="67"/>
     </row>
     <row r="158" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A158" s="78"/>
-      <c r="B158" s="79"/>
-      <c r="C158" s="79"/>
-      <c r="D158" s="79"/>
-      <c r="E158" s="79"/>
-      <c r="F158" s="80"/>
-      <c r="G158" s="81"/>
-      <c r="H158" s="81"/>
-      <c r="I158" s="81"/>
-      <c r="J158" s="81"/>
-      <c r="K158" s="81"/>
-      <c r="L158" s="82"/>
-      <c r="M158" s="82"/>
-      <c r="N158" s="82"/>
-      <c r="O158" s="82"/>
-      <c r="P158" s="81"/>
-      <c r="Q158" s="81"/>
-      <c r="R158" s="81"/>
-      <c r="S158" s="81"/>
-      <c r="T158" s="82"/>
-      <c r="U158" s="82"/>
-      <c r="V158" s="82"/>
-      <c r="W158" s="82"/>
-      <c r="X158" s="81"/>
-      <c r="Y158" s="81"/>
-      <c r="Z158" s="81"/>
-      <c r="AA158" s="82"/>
-      <c r="AB158" s="82"/>
-      <c r="AC158" s="83"/>
-      <c r="AD158" s="82"/>
-      <c r="AE158" s="22"/>
+      <c r="A158" s="79"/>
+      <c r="B158" s="80"/>
+      <c r="C158" s="80"/>
+      <c r="D158" s="80"/>
+      <c r="E158" s="80"/>
+      <c r="F158" s="81"/>
+      <c r="G158" s="82"/>
+      <c r="H158" s="82"/>
+      <c r="I158" s="82"/>
+      <c r="J158" s="82"/>
+      <c r="K158" s="82"/>
+      <c r="L158" s="83"/>
+      <c r="M158" s="83"/>
+      <c r="N158" s="83"/>
+      <c r="O158" s="83"/>
+      <c r="P158" s="82"/>
+      <c r="Q158" s="82"/>
+      <c r="R158" s="82"/>
+      <c r="S158" s="82"/>
+      <c r="T158" s="83"/>
+      <c r="U158" s="83"/>
+      <c r="V158" s="83"/>
+      <c r="W158" s="83"/>
+      <c r="X158" s="82"/>
+      <c r="Y158" s="82"/>
+      <c r="Z158" s="82"/>
+      <c r="AA158" s="83"/>
+      <c r="AB158" s="83"/>
+      <c r="AC158" s="84"/>
+      <c r="AD158" s="83"/>
+      <c r="AE158" s="67"/>
     </row>
     <row r="159" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A159" s="78"/>
-      <c r="B159" s="79"/>
-      <c r="C159" s="79"/>
-      <c r="D159" s="79"/>
-      <c r="E159" s="79"/>
-      <c r="F159" s="80"/>
-      <c r="G159" s="81"/>
-      <c r="H159" s="81"/>
-      <c r="I159" s="81"/>
-      <c r="J159" s="81"/>
-      <c r="K159" s="81"/>
-      <c r="L159" s="82"/>
-      <c r="M159" s="82"/>
-      <c r="N159" s="82"/>
-      <c r="O159" s="82"/>
-      <c r="P159" s="81"/>
-      <c r="Q159" s="81"/>
-      <c r="R159" s="81"/>
-      <c r="S159" s="81"/>
-      <c r="T159" s="82"/>
-      <c r="U159" s="82"/>
-      <c r="V159" s="82"/>
-      <c r="W159" s="82"/>
-      <c r="X159" s="81"/>
-      <c r="Y159" s="81"/>
-      <c r="Z159" s="81"/>
-      <c r="AA159" s="82"/>
-      <c r="AB159" s="82"/>
-      <c r="AC159" s="83"/>
-      <c r="AD159" s="82"/>
-      <c r="AE159" s="22"/>
+      <c r="A159" s="79"/>
+      <c r="B159" s="80"/>
+      <c r="C159" s="80"/>
+      <c r="D159" s="80"/>
+      <c r="E159" s="80"/>
+      <c r="F159" s="81"/>
+      <c r="G159" s="82"/>
+      <c r="H159" s="82"/>
+      <c r="I159" s="82"/>
+      <c r="J159" s="82"/>
+      <c r="K159" s="82"/>
+      <c r="L159" s="83"/>
+      <c r="M159" s="83"/>
+      <c r="N159" s="83"/>
+      <c r="O159" s="83"/>
+      <c r="P159" s="82"/>
+      <c r="Q159" s="82"/>
+      <c r="R159" s="82"/>
+      <c r="S159" s="82"/>
+      <c r="T159" s="83"/>
+      <c r="U159" s="83"/>
+      <c r="V159" s="83"/>
+      <c r="W159" s="83"/>
+      <c r="X159" s="82"/>
+      <c r="Y159" s="82"/>
+      <c r="Z159" s="82"/>
+      <c r="AA159" s="83"/>
+      <c r="AB159" s="83"/>
+      <c r="AC159" s="84"/>
+      <c r="AD159" s="83"/>
+      <c r="AE159" s="67"/>
     </row>
     <row r="160" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A160" s="78"/>
-      <c r="B160" s="79"/>
-      <c r="C160" s="79"/>
-      <c r="D160" s="79"/>
-      <c r="E160" s="79"/>
-      <c r="F160" s="80"/>
-      <c r="G160" s="81"/>
-      <c r="H160" s="81"/>
-      <c r="I160" s="81"/>
-      <c r="J160" s="81"/>
-      <c r="K160" s="81"/>
-      <c r="L160" s="82"/>
-      <c r="M160" s="82"/>
-      <c r="N160" s="82"/>
-      <c r="O160" s="82"/>
-      <c r="P160" s="81"/>
-      <c r="Q160" s="81"/>
-      <c r="R160" s="81"/>
-      <c r="S160" s="81"/>
-      <c r="T160" s="82"/>
-      <c r="U160" s="82"/>
-      <c r="V160" s="82"/>
-      <c r="W160" s="82"/>
-      <c r="X160" s="81"/>
-      <c r="Y160" s="81"/>
-      <c r="Z160" s="81"/>
-      <c r="AA160" s="82"/>
-      <c r="AB160" s="82"/>
-      <c r="AC160" s="83"/>
-      <c r="AD160" s="82"/>
-      <c r="AE160" s="22"/>
+      <c r="A160" s="79"/>
+      <c r="B160" s="80"/>
+      <c r="C160" s="80"/>
+      <c r="D160" s="80"/>
+      <c r="E160" s="80"/>
+      <c r="F160" s="81"/>
+      <c r="G160" s="82"/>
+      <c r="H160" s="82"/>
+      <c r="I160" s="82"/>
+      <c r="J160" s="82"/>
+      <c r="K160" s="82"/>
+      <c r="L160" s="83"/>
+      <c r="M160" s="83"/>
+      <c r="N160" s="83"/>
+      <c r="O160" s="83"/>
+      <c r="P160" s="82"/>
+      <c r="Q160" s="82"/>
+      <c r="R160" s="82"/>
+      <c r="S160" s="82"/>
+      <c r="T160" s="83"/>
+      <c r="U160" s="83"/>
+      <c r="V160" s="83"/>
+      <c r="W160" s="83"/>
+      <c r="X160" s="82"/>
+      <c r="Y160" s="82"/>
+      <c r="Z160" s="82"/>
+      <c r="AA160" s="83"/>
+      <c r="AB160" s="83"/>
+      <c r="AC160" s="84"/>
+      <c r="AD160" s="83"/>
+      <c r="AE160" s="67"/>
     </row>
     <row r="161" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A161" s="78"/>
-      <c r="B161" s="79"/>
-      <c r="C161" s="79"/>
-      <c r="D161" s="79"/>
-      <c r="E161" s="79"/>
-      <c r="F161" s="80"/>
-      <c r="G161" s="81"/>
-      <c r="H161" s="81"/>
-      <c r="I161" s="81"/>
-      <c r="J161" s="81"/>
-      <c r="K161" s="81"/>
-      <c r="L161" s="82"/>
-      <c r="M161" s="82"/>
-      <c r="N161" s="82"/>
-      <c r="O161" s="82"/>
-      <c r="P161" s="81"/>
-      <c r="Q161" s="81"/>
-      <c r="R161" s="81"/>
-      <c r="S161" s="81"/>
-      <c r="T161" s="82"/>
-      <c r="U161" s="82"/>
-      <c r="V161" s="82"/>
-      <c r="W161" s="82"/>
-      <c r="X161" s="81"/>
-      <c r="Y161" s="81"/>
-      <c r="Z161" s="81"/>
-      <c r="AA161" s="82"/>
-      <c r="AB161" s="82"/>
-      <c r="AC161" s="83"/>
-      <c r="AD161" s="82"/>
-      <c r="AE161" s="22"/>
+      <c r="A161" s="79"/>
+      <c r="B161" s="80"/>
+      <c r="C161" s="80"/>
+      <c r="D161" s="80"/>
+      <c r="E161" s="80"/>
+      <c r="F161" s="81"/>
+      <c r="G161" s="82"/>
+      <c r="H161" s="82"/>
+      <c r="I161" s="82"/>
+      <c r="J161" s="82"/>
+      <c r="K161" s="82"/>
+      <c r="L161" s="83"/>
+      <c r="M161" s="83"/>
+      <c r="N161" s="83"/>
+      <c r="O161" s="83"/>
+      <c r="P161" s="82"/>
+      <c r="Q161" s="82"/>
+      <c r="R161" s="82"/>
+      <c r="S161" s="82"/>
+      <c r="T161" s="83"/>
+      <c r="U161" s="83"/>
+      <c r="V161" s="83"/>
+      <c r="W161" s="83"/>
+      <c r="X161" s="82"/>
+      <c r="Y161" s="82"/>
+      <c r="Z161" s="82"/>
+      <c r="AA161" s="83"/>
+      <c r="AB161" s="83"/>
+      <c r="AC161" s="84"/>
+      <c r="AD161" s="83"/>
+      <c r="AE161" s="67"/>
     </row>
     <row r="162" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A162" s="78"/>
-      <c r="B162" s="79"/>
-      <c r="C162" s="79"/>
-      <c r="D162" s="79"/>
-      <c r="E162" s="79"/>
-      <c r="F162" s="80"/>
-      <c r="G162" s="81"/>
-      <c r="H162" s="81"/>
-      <c r="I162" s="81"/>
-      <c r="J162" s="81"/>
-      <c r="K162" s="81"/>
-      <c r="L162" s="82"/>
-      <c r="M162" s="82"/>
-      <c r="N162" s="82"/>
-      <c r="O162" s="82"/>
-      <c r="P162" s="81"/>
-      <c r="Q162" s="81"/>
-      <c r="R162" s="81"/>
-      <c r="S162" s="81"/>
-      <c r="T162" s="82"/>
-      <c r="U162" s="82"/>
-      <c r="V162" s="82"/>
-      <c r="W162" s="82"/>
-      <c r="X162" s="81"/>
-      <c r="Y162" s="81"/>
-      <c r="Z162" s="81"/>
-      <c r="AA162" s="82"/>
-      <c r="AB162" s="82"/>
-      <c r="AC162" s="83"/>
-      <c r="AD162" s="82"/>
-      <c r="AE162" s="22"/>
+      <c r="A162" s="79"/>
+      <c r="B162" s="80"/>
+      <c r="C162" s="80"/>
+      <c r="D162" s="80"/>
+      <c r="E162" s="80"/>
+      <c r="F162" s="81"/>
+      <c r="G162" s="82"/>
+      <c r="H162" s="82"/>
+      <c r="I162" s="82"/>
+      <c r="J162" s="82"/>
+      <c r="K162" s="82"/>
+      <c r="L162" s="83"/>
+      <c r="M162" s="83"/>
+      <c r="N162" s="83"/>
+      <c r="O162" s="83"/>
+      <c r="P162" s="82"/>
+      <c r="Q162" s="82"/>
+      <c r="R162" s="82"/>
+      <c r="S162" s="82"/>
+      <c r="T162" s="83"/>
+      <c r="U162" s="83"/>
+      <c r="V162" s="83"/>
+      <c r="W162" s="83"/>
+      <c r="X162" s="82"/>
+      <c r="Y162" s="82"/>
+      <c r="Z162" s="82"/>
+      <c r="AA162" s="83"/>
+      <c r="AB162" s="83"/>
+      <c r="AC162" s="84"/>
+      <c r="AD162" s="83"/>
+      <c r="AE162" s="67"/>
     </row>
     <row r="163" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A163" s="78"/>
-      <c r="B163" s="79"/>
-      <c r="C163" s="79"/>
-      <c r="D163" s="79"/>
-      <c r="E163" s="79"/>
-      <c r="F163" s="80"/>
-      <c r="G163" s="81"/>
-      <c r="H163" s="81"/>
-      <c r="I163" s="81"/>
-      <c r="J163" s="81"/>
-      <c r="K163" s="81"/>
-      <c r="L163" s="82"/>
-      <c r="M163" s="82"/>
-      <c r="N163" s="82"/>
-      <c r="O163" s="82"/>
-      <c r="P163" s="81"/>
-      <c r="Q163" s="81"/>
-      <c r="R163" s="81"/>
-      <c r="S163" s="81"/>
-      <c r="T163" s="82"/>
-      <c r="U163" s="82"/>
-      <c r="V163" s="82"/>
-      <c r="W163" s="82"/>
-      <c r="X163" s="81"/>
-      <c r="Y163" s="81"/>
-      <c r="Z163" s="81"/>
-      <c r="AA163" s="82"/>
-      <c r="AB163" s="82"/>
-      <c r="AC163" s="83"/>
-      <c r="AD163" s="82"/>
-      <c r="AE163" s="22"/>
+      <c r="A163" s="79"/>
+      <c r="B163" s="80"/>
+      <c r="C163" s="80"/>
+      <c r="D163" s="80"/>
+      <c r="E163" s="80"/>
+      <c r="F163" s="81"/>
+      <c r="G163" s="82"/>
+      <c r="H163" s="82"/>
+      <c r="I163" s="82"/>
+      <c r="J163" s="82"/>
+      <c r="K163" s="82"/>
+      <c r="L163" s="83"/>
+      <c r="M163" s="83"/>
+      <c r="N163" s="83"/>
+      <c r="O163" s="83"/>
+      <c r="P163" s="82"/>
+      <c r="Q163" s="82"/>
+      <c r="R163" s="82"/>
+      <c r="S163" s="82"/>
+      <c r="T163" s="83"/>
+      <c r="U163" s="83"/>
+      <c r="V163" s="83"/>
+      <c r="W163" s="83"/>
+      <c r="X163" s="82"/>
+      <c r="Y163" s="82"/>
+      <c r="Z163" s="82"/>
+      <c r="AA163" s="83"/>
+      <c r="AB163" s="83"/>
+      <c r="AC163" s="84"/>
+      <c r="AD163" s="83"/>
+      <c r="AE163" s="67"/>
     </row>
     <row r="164" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A164" s="78"/>
-      <c r="B164" s="79"/>
-      <c r="C164" s="79"/>
-      <c r="D164" s="79"/>
-      <c r="E164" s="79"/>
-      <c r="F164" s="80"/>
-      <c r="G164" s="81"/>
-      <c r="H164" s="81"/>
-      <c r="I164" s="81"/>
-      <c r="J164" s="81"/>
-      <c r="K164" s="81"/>
-      <c r="L164" s="82"/>
-      <c r="M164" s="82"/>
-      <c r="N164" s="82"/>
-      <c r="O164" s="82"/>
-      <c r="P164" s="81"/>
-      <c r="Q164" s="81"/>
-      <c r="R164" s="81"/>
-      <c r="S164" s="81"/>
-      <c r="T164" s="82"/>
-      <c r="U164" s="82"/>
-      <c r="V164" s="82"/>
-      <c r="W164" s="82"/>
-      <c r="X164" s="81"/>
-      <c r="Y164" s="81"/>
-      <c r="Z164" s="81"/>
-      <c r="AA164" s="82"/>
-      <c r="AB164" s="82"/>
-      <c r="AC164" s="83"/>
-      <c r="AD164" s="82"/>
-      <c r="AE164" s="22"/>
+      <c r="A164" s="79"/>
+      <c r="B164" s="80"/>
+      <c r="C164" s="80"/>
+      <c r="D164" s="80"/>
+      <c r="E164" s="80"/>
+      <c r="F164" s="81"/>
+      <c r="G164" s="82"/>
+      <c r="H164" s="82"/>
+      <c r="I164" s="82"/>
+      <c r="J164" s="82"/>
+      <c r="K164" s="82"/>
+      <c r="L164" s="83"/>
+      <c r="M164" s="83"/>
+      <c r="N164" s="83"/>
+      <c r="O164" s="83"/>
+      <c r="P164" s="82"/>
+      <c r="Q164" s="82"/>
+      <c r="R164" s="82"/>
+      <c r="S164" s="82"/>
+      <c r="T164" s="83"/>
+      <c r="U164" s="83"/>
+      <c r="V164" s="83"/>
+      <c r="W164" s="83"/>
+      <c r="X164" s="82"/>
+      <c r="Y164" s="82"/>
+      <c r="Z164" s="82"/>
+      <c r="AA164" s="83"/>
+      <c r="AB164" s="83"/>
+      <c r="AC164" s="84"/>
+      <c r="AD164" s="83"/>
+      <c r="AE164" s="67"/>
     </row>
     <row r="165" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="15"/>
@@ -9459,7 +9466,7 @@
       <c r="AB165" s="15"/>
       <c r="AC165" s="41"/>
       <c r="AD165" s="15"/>
-      <c r="AE165" s="22"/>
+      <c r="AE165" s="67"/>
     </row>
     <row r="166" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="15"/>
